--- a/v0.4.4-埋点表清单.xlsx
+++ b/v0.4.4-埋点表清单.xlsx
@@ -8,15 +8,16 @@
   </bookViews>
   <sheets>
     <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="A-连接与会话" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="B-钓位与鱼塘" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="C-状态机" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="D-咬钩与产出" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="D-成长与进度" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="D-装备" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="D-风险事件" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="E-系统性能" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="慢测验证" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="落库格式" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="A-连接与会话" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="B-钓位与鱼塘" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="C-状态机" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="D-咬钩与产出" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="D-成长与进度" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="D-装备" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="D-风险事件" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="E-系统性能" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="慢测验证" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,17 +438,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -511,24 +512,18 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>日志</t>
+          <t>metrics+日志</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>socket 建连成功</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>ts
-playerId
-socketId</t>
-        </is>
-      </c>
+          <t>socket 建连成功，此时尚未绑定玩家</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>{"eventType":"socket_connect"}</t>
+          <t>{"socketId":"sock-1","reason":"socket_connected","correlationId":"corr-1"}</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -543,7 +538,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>fishingObservability.ts</t>
+          <t>socketLifecycle.ts</t>
         </is>
       </c>
     </row>
@@ -555,7 +550,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>socket_disconnect</t>
+          <t>socket_connect_error</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -565,19 +560,13 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>socket 断开</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>ts
-playerId
-reason</t>
-        </is>
-      </c>
+          <t>引擎 connection_error</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>{"eventType":"disconnect"}</t>
+          <t>{"socketId":"sock-1","reason":"xhr poll error","code":1}</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -587,12 +576,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>已实现(别名disconnect)</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>fishingStateMachine.ts</t>
+          <t>socketLifecycle.ts</t>
         </is>
       </c>
     </row>
@@ -604,28 +593,28 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>socket_connect_error</t>
+          <t>socket_disconnect</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>日志</t>
+          <t>metrics+日志</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>建连失败</t>
+          <t>在塘玩家 socket 断开，进入宽限</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>ts
-reason</t>
+          <t>playerId
+pondId</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"userId":"u1","spotId":"spot-1","fishingPhase":"waiting","reason":"socket_disconnect"}</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -640,7 +629,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>socketLifecycle.ts</t>
+          <t>fishingStateMachine.ts</t>
         </is>
       </c>
     </row>
@@ -652,43 +641,43 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>join_pond_attempt</t>
+          <t>disconnect</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>日志</t>
+          <t>metrics</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>收到 join_pond</t>
+          <t>旧断线名。生产不再写，测试与历史查询仍认</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>pondId
-playerId</t>
+          <t>playerId
+pondId</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"socketId":"sock-1","reason":"transport"}</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已废弃</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>gameState.ts</t>
+          <t>fishingStateMachine.ts</t>
         </is>
       </c>
     </row>
@@ -700,7 +689,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>join_pond_success</t>
+          <t>reconnect</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -710,18 +699,18 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>join/reconnect 成功</t>
+          <t>宽限期内重连回塘</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>pondId
-joinKind</t>
+          <t>playerId
+pondId</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>{"joinKind":"reconnect"}</t>
+          <t>{"userId":"u1","spotId":"spot-1","fishingPhase":"waiting","reason":"socket_reconnect"}</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -736,7 +725,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>gameState.ts</t>
+          <t>fishingStateMachine.ts</t>
         </is>
       </c>
     </row>
@@ -748,7 +737,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>join_pond_fail</t>
+          <t>disconnect_timeout</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -758,17 +747,18 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>join 失败</t>
+          <t>断线宽限超时清场</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>ackError</t>
+          <t>playerId
+pondId</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"userId":"u1","spotId":"spot-1","fishingPhase":"disconnected","reason":"disconnect_timeout"}</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -783,7 +773,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>gameState.ts</t>
+          <t>fishingStateMachine.ts</t>
         </is>
       </c>
     </row>
@@ -795,7 +785,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>leave_pond</t>
+          <t>join_pond_attempt</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -805,17 +795,18 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>主动离塘</t>
+          <t>收到 join_pond。身份会再抄进 payload</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>playerId
+pondId</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>{"reason":"user_leave"}</t>
+          <t>{"socketId":"sock-1","reason":"join_pond_attempt","playerId":"p1","pondId":"pond-calm"}</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -830,7 +821,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>gameState.ts</t>
+          <t>socketPondHandlers.ts</t>
         </is>
       </c>
     </row>
@@ -842,7 +833,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>disconnect_timeout</t>
+          <t>join_pond_success</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -852,7 +843,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60s 未重连清场</t>
+          <t>进塘或重连成功。joinKind=fresh|reconnect</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -863,7 +854,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"userId":"u1","socketId":"sock-1","spotId":null,"fishingPhase":"idle","reason":"join_pond_success","joinKind":"fresh","playerId":"p1","pondId":"pond-calm"}</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -878,7 +869,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>fishingStateMachine.ts</t>
+          <t>socketPondHandlers.ts</t>
         </is>
       </c>
     </row>
@@ -890,149 +881,151 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>join_pond_fail</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>metrics+日志</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>进塘失败。reason=return_fee_mode|pond_access|police_ban|pond_full 等</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>{"socketId":"sock-1","reason":"pond_full","ackError":"鱼塘已满（最多 20 人）"}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>socketPondHandlers.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>A连接会话</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>leave_pond</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>主动离塘带会话计数；巡警罚款离塘 reason=police_fine</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>{"reason":"user_explicit","spotId":"spot-1","fishingPhase":"seated","sessionHooks":1,"sessionEscapes":0,"sessionMissTicks":4,"missTicksSinceLastHook":4}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>socketPondHandlers.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>A连接会话</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>session_rebound</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>日志</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>playerId 绑定新 socket</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>同一 playerId 绑到新 socket。不进 fishing_metrics</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>playerId
 socketId</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>{"playerId":"p1","socketId":"sock-2","previousSocketId":"sock-1","reason":"session_registry_bind_player","correlationId":"corr-1"}</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>sessionRegistry.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>B钓位鱼塘</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>spot_take_success</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>占座成功</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>spotId</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>gameState.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>B钓位鱼塘</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>spot_take_fail</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>占座失败</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>reason</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>gameState.ts</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>B钓位鱼塘</t>
+          <t>A连接会话</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>spot_release</t>
+          <t>server_start</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1042,23 +1035,18 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>释放钓位</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>spotId
-reason</t>
-        </is>
-      </c>
+          <t>HTTP 开始监听</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"pid":1234,"startedAt":1710000000000,"reason":"unknown"}</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1068,19 +1056,19 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>gameState.ts</t>
+          <t>index.ts</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>B钓位鱼塘</t>
+          <t>A连接会话</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>pond_full_reject</t>
+          <t>server_stop</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1090,22 +1078,18 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>鱼塘满</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>pondId</t>
-        </is>
-      </c>
+          <t>收到 SIGINT/SIGTERM 或致命错误，开始停机</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"pid":1234,"uptimeSec":3600,"reason":"SIGTERM","startedAt":1710000000000}</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1115,7 +1099,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>gameState.ts</t>
+          <t>index.ts</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1111,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>bot_evicted_for_human</t>
+          <t>spot_take_success</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1137,17 +1121,19 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>踢 bot 腾位</t>
+          <t>占座成功</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>botUserId</t>
+          <t>playerId
+pondId
+spotId</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"userId":"u1","socketId":"sock-1","spotId":"spot-1","fishingPhase":"seated","eventId":"spot_take:u1:spot-1"}</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1162,7 +1148,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>gameState.ts</t>
+          <t>pondSession.ts</t>
         </is>
       </c>
     </row>
@@ -1174,33 +1160,29 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>pond_ecology_catchup</t>
+          <t>spot_take_fail</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>日志</t>
+          <t>metrics</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>空鱼塘唤醒时事务化补算生态</t>
+          <t>钓位已被占用</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>pondId
-offlineMs
-replaySteps
-migrated
-supplemented
-durationMs
-catchupCompacted</t>
+          <t>playerId
+pondId
+spotId</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>{"catchupCompacted":false,"replaySteps":2}</t>
+          <t>{"userId":"u1","spotId":"spot-1","reason":"occupied_by_human","occupantUserId":"u2","eventId":"spot_fail:u1:spot-1"}</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1215,342 +1197,347 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>pondEcology.ts</t>
+          <t>pondSession.ts</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>B钓位鱼塘</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>spot_release</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>离席或离塘释放钓位。reason=leave_spot|leave_pond</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId
+spotId</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>{"userId":"u1","spotId":"spot-1","fishingPhase":"idle","reason":"leave_spot","eventId":"spot_release:u1:spot-1:leave_spot"}</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>pondSession.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>B钓位鱼塘</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>pond_full_reject</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>人数达到上限</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>{"socketId":"sock-1","reason":"max_pond_users","maxPondUsers":20,"eventId":"pond_full:p1:1710000000000"}</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>pondSession.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>B钓位鱼塘</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>bot_evicted_for_human</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>给人腾位。player_id 列是被挤走的 bot</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>pondId</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>{"userId":"bot-user","reason":"pond_full_or_spot_pressure","eventId":"bot_evict:bot-user:1710000000000"}</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>pondUserManager.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>B钓位鱼塘</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>pond_ecology_catchup</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>日志</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>空鱼塘唤醒补算。只打日志，不进 fishing_metrics</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>pondId</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>{"eventType":"pond_ecology_catchup","pondId":"pond-calm","offlineMs":60000,"replaySteps":2,"migrated":0,"supplemented":1,"durationMs":12,"catchupCompacted":false}</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>pondEcology.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>B钓位鱼塘</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>pond_ecology_catchup_failed</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>日志</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>进塘前补算失败。只打日志</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>pondId</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>{"eventType":"pond_ecology_catchup_failed","pondId":"pond-calm","playerId":"p1"}</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>socketPondHandlers.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>C状态机</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>fishing_phase_transition</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>metrics+日志</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>phase 变更；D-L2-16 metrics 仅短码 f/t/c；ADMIN-OBS-1.3 默认 bot 不落库（METRICS_BOT_PHASE=1 恢复）；日志仍用全称</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>f
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>相位变更。库内仅 f/t/c；日志用全名。默认 bot 不落库（METRICS_BOT_PHASE=1 恢复）。f=-1 无来源；0 idle 1 seated 2 baiting 3 casting 4 waiting 5 hooked 6 resolving 7 stopping 8 disconnected 9 groundbaiting</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId
+f
 t
 c</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>{"f":4,"t":5,"c":"bite_hook"}</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>fishingObservability.ts</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>C状态机</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>phase_transition_invalid</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>日志+metrics</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>非法跳转；metrics 短码 f/t/c；日志可读全称</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>f
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>metrics+日志</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>非法相位跳转。库内仅 f/t/c；日志保留全名。默认 bot 不落库</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId
+f
 t
 c</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>{"f":0,"t":5,"c":"bite_hook"}</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>fishingStateMachine.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>D咬钩产出</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>bite_tick_miss</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>waiting 未咬钩（D-L2-15 默认不落库；METRICS_BITE_TICK_PERSIST=1）</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>pondId</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>已废弃默认</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>fishingStateMachine.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>D咬钩产出</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>bite_tick_hit</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>waiting 咬钩（D-L2-15 默认不落库，并入 bite_hook）</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>speciesId
-quality</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>已废弃默认</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>fishingStateMachine.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>D咬钩产出</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>bite_hook</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>上钩+会话累计（sessionHooks/Escapes/MissTicks）</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>sessionHooks
-sessionMissTicks</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>fishingStateMachine.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>D咬钩产出</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>pending_catch_created</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>待领取创建</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>fishId</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>inventory.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>D咬钩产出</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>pending_catch_accept</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>领取成功</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>fishId</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>已实现(别名catch_accept)</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>socketPondHandlers.ts</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1549,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>pending_catch_expired</t>
+          <t>bite_tick_miss</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1572,17 +1559,18 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>待领取超时</t>
+          <t>waiting 未咬钩。默认不落库；METRICS_BITE_TICK_PERSIST=1 恢复</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>fishId</t>
+          <t>playerId
+pondId</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"userId":"u1","spotId":"spot-1","reason":"empty"}</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1592,12 +1580,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已废弃默认</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>inventory.ts</t>
+          <t>fishingStateMachine.ts</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1597,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>bait_depleted</t>
+          <t>bite_tick_hit</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1619,17 +1607,18 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>饵耗尽</t>
+          <t>waiting 咬钩 tick。默认不落库，语义并入 bite_hook；METRICS_BITE_TICK_PERSIST=1 恢复</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>baitId</t>
+          <t>playerId
+pondId</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"userId":"u1","spotId":"spot-1","speciesId":"crucian","quality":"green","sizeM":0.2,"hookDurationMs":8000}</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1639,7 +1628,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已废弃默认</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1656,7 +1645,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>escape</t>
+          <t>bite_hook</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1666,18 +1655,18 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>脱钩+会话累计</t>
+          <t>上钩，并写入会话累计</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sessionEscapes
-sessionHooks</t>
+          <t>playerId
+pondId</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"speciesId":"crucian","quality":"green","sessionHooks":1,"sessionEscapes":0,"sessionMissTicks":4,"missTicksSinceLastHook":4,"waitingMsSinceLastHook":180000}</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1704,7 +1693,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>fishing_start</t>
+          <t>escape</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1714,22 +1703,23 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>开始钓鱼</t>
+          <t>脱钩，并写入会话累计</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>pondId</t>
+          <t>playerId
+pondId</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"sessionHooks":1,"sessionEscapes":1,"sessionMissTicks":4}</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1751,7 +1741,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>fishing_stop</t>
+          <t>escape_streak</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1761,17 +1751,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>停止钓鱼</t>
+          <t>同一玩家连续脱钩达到 3 次时另写一行</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>pondId</t>
+          <t>playerId</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"streak":3,"eventId":"escape_streak:p1:1710000000000"}</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1786,7 +1776,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>fishingStateMachine.ts</t>
+          <t>fishingMetrics.ts</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1788,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>abandon_fishing</t>
+          <t>fishing_start</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1808,12 +1798,13 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>&lt;30s 停止</t>
+          <t>开始一局。payload 为空</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>pondId</t>
+          <t>playerId
+pondId</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1833,19 +1824,19 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>fishingMetrics.ts</t>
+          <t>fishingStateMachine.ts</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>D成长进度</t>
+          <t>D咬钩产出</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>admission_fee_charged</t>
+          <t>fishing_stop</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1855,24 +1846,23 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>收费塘满2h扣费成功</t>
+          <t>收杆。payload 为会话计数</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
           <t>playerId
-pondId
-feePer2h</t>
+pondId</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>{"feePer2h":200,"chargeIndex":1}</t>
+          <t>{"sessionHooks":2,"sessionEscapes":1,"sessionMissTicks":6,"missTicksSinceLastHook":2}</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1882,19 +1872,19 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>playerProgress.ts</t>
+          <t>fishingStateMachine.ts</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>D成长进度</t>
+          <t>D咬钩产出</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>fishing_stopped_insufficient_gold</t>
+          <t>abandon_fishing</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1904,70 +1894,70 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>金币不足停钓</t>
+          <t>fishing_start 后 30 秒内 fishing_stop。payload 为空</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>fishingMetrics.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>D咬钩产出</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>pending_catch_created</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>锁定待结算的咬钩鱼</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>playerId
 pondId</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>{"feePer2h":200}</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>playerProgress.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>D成长进度</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>onboarding_completed</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>新手引导完成</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>playerId</t>
-        </is>
-      </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>{"pondId":"pond-novice"}</t>
+          <t>{"userId":"u1","pondFishId":"fish-1","speciesId":"crucian","quality":"green","sizeM":0.2,"hookDurationMs":8000}</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1977,19 +1967,19 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>playerProgress.ts</t>
+          <t>inventory.ts</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>D成长进度</t>
+          <t>D咬钩产出</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>pond_proficiency_capped</t>
+          <t>pending_catch_accept</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1999,7 +1989,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>塘熟练度满/锁满停发塘XP</t>
+          <t>收鱼入包。dedup_key=pending_catch_accept:{eventId}</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2010,7 +2000,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>{"source":"catch"}</t>
+          <t>{"speciesId":"crucian","quality":"green","sizeM":0.2,"eventId":"catch-1","auto":false}</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2025,19 +2015,19 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>playerProgress.ts</t>
+          <t>catchSettlement.ts</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>D装备</t>
+          <t>D咬钩产出</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>bait_use</t>
+          <t>pending_catch_expired</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2047,24 +2037,23 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>咬钩使用进阶饵扣金</t>
+          <t>待结算超时释放</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
           <t>playerId
-baitId
-cost</t>
+pondId</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>{"baitId":"bait-veg","cost":15}</t>
+          <t>{"userId":"u1","pondFishId":"fish-1","speciesId":"crucian","quality":"green","sizeM":0.2}</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2074,19 +2063,19 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>gear.ts</t>
+          <t>inventory.ts</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>D装备</t>
+          <t>D咬钩产出</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>rod_buy</t>
+          <t>catch_accept</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2096,45 +2085,45 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>购买钓竿</t>
+          <t>旧收鱼名。生产改写 pending_catch_accept；历史榜与测试仍认</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
           <t>playerId
-rodId</t>
+pondId</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>{"rodId":"rod-tai","cost":2500}</t>
+          <t>{"fishId":"fish-1","speciesId":"crucian","quality":"green","sizeM":0.2}</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已废弃</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>shop.ts</t>
+          <t>catchSettlement.ts</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>D装备</t>
+          <t>D咬钩产出</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>rod_broke</t>
+          <t>bait_depleted</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2144,23 +2133,23 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>超规格满N次销毁钓竿</t>
+          <t>饵尽。reason=auto_switch_after_depletion|bait_insufficient</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
           <t>playerId
-rodId</t>
+pondId</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>{"sizeM":0.5,"oversizeLandings":3}</t>
+          <t>{"userId":"u1","socketId":"sock-1","previousBaitId":"bait-worm","reason":"auto_switch_after_depletion"}</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2170,19 +2159,19 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>gear.ts</t>
+          <t>fishingStateMachine.ts</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>D装备</t>
+          <t>D成长进度</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>vessel_buy</t>
+          <t>admission_fee_charged</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2192,23 +2181,23 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>购买船具（不可使用）</t>
+          <t>收费塘满 2 小时扣费成功</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
           <t>playerId
-vesselId</t>
+pondId</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>{"vesselId":"vessel-raft","cost":15000}</t>
+          <t>{"feePer2h":200,"returnFeeMode":"sell_only","chargeIndex":1,"progressMs":7200000,"coinsAfter":800}</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2218,19 +2207,19 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>shop.ts</t>
+          <t>playerProgress.ts</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>D风险</t>
+          <t>D成长进度</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>forbidden_pond_fine</t>
+          <t>fishing_stopped_insufficient_gold</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2240,7 +2229,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>禁止塘巡警超时罚款+当日禁钓</t>
+          <t>金币不够支付下一档入场费</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2251,7 +2240,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>{"charged":800,"coinsAfter":0}</t>
+          <t>{"feePer2h":200,"returnFeeMode":"sell_only","charges":1,"progressMs":14400000,"coins":0}</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -2266,19 +2255,19 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>forbiddenPolice.ts</t>
+          <t>playerProgress.ts</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>D风险</t>
+          <t>D成长进度</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>forbidden_pond_escaped</t>
+          <t>onboarding_completed</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2288,265 +2277,264 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>禁止塘巡警时限内离塘免罚，2h禁入</t>
+          <t>新手引导完成。pond_id 列固定 pond-novice</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>{"completedAt":1710000000000}</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>playerProgress.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>D成长进度</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>pond_proficiency_capped</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>塘熟练度封顶。source=catch|return|duration</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>playerId
 pondId</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>{"untilMs":0}</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>forbiddenPolice.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>{"pondLevel":10,"playerLevel":8,"source":"catch"}</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>playerProgress.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>D成长进度</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>gameplay_debug_action</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>玩法 Debug 菜单操作</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>玩法 Debug 菜单</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>playerId
 action</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>{"action":"level_up","ok":true}</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>{"action":"level_up","ok":true,"message":"ok"}</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
         <is>
           <t>gameplayDebug.ts</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>D成长进度</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>fish_returned_to_pond</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>回鱼入塘增重并发奖</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>回鱼入塘。自动回鱼时再写 fish_auto_returned</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>playerId
 pondId</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>{"speciesId":"crucian","sizeM":0.2,"gold":56,"sizeGainM":0.03,"auto":false}</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>{"speciesId":"crucian","sizeM":0.2,"gold":56,"sizeGainM":0.03,"quality":"green","newSizeM":0.23,"sellGold":40,"spawned":true,"auto":false}</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>returnFish.ts</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>D成长进度</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>return_fee_mode_selected</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>进塘双价模式选择</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>fish_auto_returned</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>达标自动回塘。payload 与 fish_returned_to_pond 相同且 auto=true</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>playerId
 pondId</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>{"mode":"auto_return","feePer2h":350}</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>{"speciesId":"crucian","sizeM":0.28,"gold":120,"sizeGainM":0.04,"quality":"green","newSizeM":0.32,"sellGold":80,"spawned":true,"auto":true}</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>socketPondHandlers.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>returnFish.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>D成长进度</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>fish_auto_returned</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>达标鱼自动回塘</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>return_fee_mode_selected</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>进塘选定卖鱼或自动回鱼</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>playerId
 pondId</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>{"speciesId":"crucian","sizeM":0.28,"gold":120,"auto":true}</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>{"mode":"auto_return","feePer2h":350}</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>returnFish.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>D装备</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>groundbait_cast_started</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>开始打窝扣金</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>playerId
-groundbaitId</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>{"costGold":30,"stackBefore":0}</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t>已实现</t>
@@ -2554,534 +2542,1143 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>groundbait.ts</t>
+          <t>socketPondHandlers.ts</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>D成长进度</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>gold_earn</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>卖鱼 source=fish_sell；回鱼 source=fish_return</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>{"amount":56,"source":"fish_sell","fishId":"inv-1","quality":"green","sizeM":0.2}</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>socialRoutes.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>D成长进度</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>achievement_unlocked</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>成就解锁</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>{"achievementId":"ach-first-catch"}</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>achievements.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>D成长进度</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>album_pin_changed</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>相册钉选。action=pin|unpin|set</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>{"pinCount":3,"action":"pin"}</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>socialRoutes.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>D成长进度</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>profile_hub_opened</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>打开自己的个人中心。tab 默认 profile</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>{"tab":"profile"}</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>socialRoutes.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
           <t>D装备</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>bait_use</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>咬钩时进阶饵扣金</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>{"baitId":"bait-veg","cost":15,"coinsAfter":985}</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>gear.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>D装备</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>bait_buy</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>旧买饵事件。接口已拒绝，无生产写入</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>{"baitId":"worm","quantity":1,"cost":500}</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>已废弃</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>shop.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>D装备</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>tackle_buy</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>旧买渔具事件。生产改写 rod_buy</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>{"tackleId":"rod-basic","cost":100}</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>已废弃</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>shop.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>D装备</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>tackle_repair</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>修理渔具</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>{"tackleId":"pro","cost":40}</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>gear.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>D装备</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>rod_buy</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>购买钓竿</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>{"rodId":"rod-tai","cost":2500}</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>shop.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>D装备</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>rod_broke</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>超规格次数达到销毁阈值</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>{"rodId":"rod-tai","sizeM":0.5,"oversizeLandings":3}</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>gear.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>D装备</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>vessel_buy</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>购买船具（不可使用）</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>{"vesselId":"vessel-raft","cost":15000}</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>shop.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>D装备</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>groundbait_cast_started</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>开始打窝扣金。不写 pond_id</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>{"groundbaitId":"gb-basic","costGold":30,"stackBefore":0}</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>groundbait.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>D装备</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>groundbait_applied</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>打窝完成叠层</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>playerId
 pondId</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>{"stackAfter":1,"biteBonus":0.006}</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>{"groundbaitId":"gb-basic","stackAfter":1,"biteBonus":0.006,"sizeBonus":0.003}</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
         <is>
           <t>groundbait.ts</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>D装备</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>groundbait_rejected</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>打窝拒绝</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>打窝被拒绝</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>{"reason":"gold","code":"INSUFFICIENT_GOLD"}</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>groundbait.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>D风险</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>forbidden_pond_fine</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>巡警超时罚款并当日禁钓</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>playerId
-reason</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>{"reason":"gold","code":"INSUFFICIENT_GOLD"}</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>groundbait.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>D成长进度</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>achievement_unlocked</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>成就解锁</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
+pondId</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>{"charged":800,"coinsAfter":0,"fineGold":800,"raidId":"raid-1"}</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>forbiddenPolice.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>D风险</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>forbidden_pond_escaped</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>时限内离塘免罚，2 小时禁入</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>playerId
-achievementId</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>{"achievementId":"ach-first-catch"}</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>achievements.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>D成长进度</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>album_pin_changed</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>相册钉选变更</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>playerId
-pinCount
-action</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>{"pinCount":3,"action":"pin"}</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>album.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>D成长进度</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>profile_hub_opened</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>打开个人中心</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>playerId
-tab</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>{"tab":"album"}</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>profileHub.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+pondId</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>{"untilMs":1710007200000,"raidId":"raid-1"}</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>forbiddenPolice.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>E性能</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>tick_fishing_phases_duration_ms</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>聚合日志</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>200ms tick 耗时</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>相位 tick 耗时。慢于 PERF_LOG_SLOW_MS 才打，默认不进 fishing_metrics</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>durationMs</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>{"eventType":"tick_fishing_phases_duration_ms","durationMs":12,"pondCount":4,"activeUsers":3,"snapshotCalls":0}</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
         <is>
           <t>serverLoops.ts</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>E性能</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>bite_check_loop_duration_ms</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>聚合日志</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>咬钩循环耗时</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>咬钩循环耗时。慢日志，不进 fishing_metrics</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>durationMs</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>{"eventType":"bite_check_loop_duration_ms","durationMs":20,"pondCount":4,"candidates":2,"triggered":1,"snapshotCalls":0}</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
         <is>
           <t>serverLoops.ts</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>E性能</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>ecology_tick_duration_ms</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>聚合日志</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>生态 tick 耗时。慢日志，不进 fishing_metrics</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>durationMs</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>{"eventType":"ecology_tick_duration_ms","durationMs":30,"pondCount":4}</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>serverLoops.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>E性能</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>snapshot_build_duration_ms</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>聚合日志</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>buildSnapshot 耗时</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>buildSnapshot 耗时。慢日志，不进 fishing_metrics</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>durationMs
 pondId</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>{"eventType":"snapshot_build_duration_ms","durationMs":8,"pondId":"pond-calm","userCount":3}</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>gameState.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>pondUserManager.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>E性能</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>socket_broadcast_fanout</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>指标+可选日志</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>广播 fanout；默认 Prometheus counter，FANOUT_LOG_INFO=1 才打 info</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>广播 fanout。Prometheus 常计；FANOUT_LOG_INFO=1 才打 info</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>fanoutCount
 channel
 pondId</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>{"eventType":"socket_broadcast_fanout","channel":"pond_user_joined","pondId":"pond-calm","fanoutCount":3}</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
         <is>
           <t>serverLoops.ts</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>E性能</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>sqlite_query_slow</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>日志</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>慢 SQL</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>label
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>SQL 慢于 SLOW_QUERY_MS（默认 30）。不进 fishing_metrics</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>queryName
+durationMs</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>{"eventType":"sqlite_query_slow","queryName":"metrics_player_timeline","durationMs":42,"thresholdMs":30,"rows":20,"ts":1710000000000}</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>db.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>E性能</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>admin_route_duration_ms</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>日志</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>每条 Admin 请求结束时 console.log，不是 logStructuredEvent</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>path
+durationMs</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>{"eventType":"admin_route_duration_ms","method":"GET","path":"/players","status":200,"durationMs":15,"ts":1710000000000}</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>admin.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>E性能</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>admin_route_slow</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>日志</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Admin 耗时达到 ADMIN_ROUTE_SLOW_MS 时另打一行 console.log</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>path
 durationMs
-rows</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
+thresholdMs</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>{"eventType":"admin_route_slow","method":"GET","path":"/players","status":200,"durationMs":800,"thresholdMs":200,"ts":1710000000000}</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>db.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>E性能</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>admin_route_duration_ms</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>日志</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>Admin 接口耗时</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>route
-durationMs</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
         <is>
           <t>admin.ts</t>
         </is>
@@ -3098,6 +3695,461 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>类别</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>事件名</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>触发时机</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>必填字段(核心)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>示例payload</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>推荐落点文件</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>E性能</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>tick_fishing_phases_duration_ms</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>聚合日志</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>相位 tick 耗时。慢于 PERF_LOG_SLOW_MS 才打，默认不进 fishing_metrics</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>durationMs</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>{"eventType":"tick_fishing_phases_duration_ms","durationMs":12,"pondCount":4,"activeUsers":3,"snapshotCalls":0}</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>serverLoops.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>E性能</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>bite_check_loop_duration_ms</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>聚合日志</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>咬钩循环耗时。慢日志，不进 fishing_metrics</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>durationMs</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>{"eventType":"bite_check_loop_duration_ms","durationMs":20,"pondCount":4,"candidates":2,"triggered":1,"snapshotCalls":0}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>serverLoops.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>E性能</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>ecology_tick_duration_ms</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>聚合日志</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>生态 tick 耗时。慢日志，不进 fishing_metrics</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>durationMs</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>{"eventType":"ecology_tick_duration_ms","durationMs":30,"pondCount":4}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>serverLoops.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>E性能</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>snapshot_build_duration_ms</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>聚合日志</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>buildSnapshot 耗时。慢日志，不进 fishing_metrics</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>durationMs
+pondId</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>{"eventType":"snapshot_build_duration_ms","durationMs":8,"pondId":"pond-calm","userCount":3}</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>pondUserManager.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>E性能</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>socket_broadcast_fanout</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>指标+可选日志</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>广播 fanout。Prometheus 常计；FANOUT_LOG_INFO=1 才打 info</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>fanoutCount
+channel
+pondId</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>{"eventType":"socket_broadcast_fanout","channel":"pond_user_joined","pondId":"pond-calm","fanoutCount":3}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>serverLoops.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>E性能</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>sqlite_query_slow</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>日志</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>SQL 慢于 SLOW_QUERY_MS（默认 30）。不进 fishing_metrics</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>queryName
+durationMs</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>{"eventType":"sqlite_query_slow","queryName":"metrics_player_timeline","durationMs":42,"thresholdMs":30,"rows":20,"ts":1710000000000}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>db.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>E性能</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>admin_route_duration_ms</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>日志</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>每条 Admin 请求结束时 console.log，不是 logStructuredEvent</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>path
+durationMs</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>{"eventType":"admin_route_duration_ms","method":"GET","path":"/players","status":200,"durationMs":15,"ts":1710000000000}</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>admin.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>E性能</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>admin_route_slow</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>日志</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Admin 耗时达到 ADMIN_ROUTE_SLOW_MS 时另打一行 console.log</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>path
+durationMs
+thresholdMs</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>{"eventType":"admin_route_slow","method":"GET","path":"/players","status":200,"durationMs":800,"thresholdMs":200,"ts":1710000000000}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>admin.ts</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -3200,496 +4252,202 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>类别</t>
+          <t>项</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>事件名</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>类型</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>触发时机</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>必填字段(核心)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>示例payload</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>优先级</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>推荐落点文件</t>
+          <t>内容</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>A连接会话</t>
+          <t>表</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>socket_connect</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>日志</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>socket 建连成功</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>ts
-playerId
-socketId</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>{"eventType":"socket_connect"}</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>fishingObservability.ts</t>
+          <t>fishing_metrics（SQLite payload 为 TEXT；Postgres payload 为 JSONB）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>A连接会话</t>
+          <t>列</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>socket_disconnect</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>metrics+日志</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>socket 断开</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>ts
-playerId
-reason</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>{"eventType":"disconnect"}</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>已实现(别名disconnect)</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>fishingStateMachine.ts</t>
+          <t>id, event_type, player_id, pond_id, payload, correlation_id, dedup_key, created_at</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>A连接会话</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>socket_connect_error</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>日志</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>建连失败</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>ts
-reason</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>socketLifecycle.ts</t>
+          <t>randomUUID()</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>A连接会话</t>
+          <t>event_type</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>join_pond_attempt</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>日志</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>收到 join_pond</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>pondId
-playerId</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>gameState.ts</t>
+          <t>与埋点表「事件名」、metrics-schema eventType 相同</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>A连接会话</t>
+          <t>player_id / pond_id</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>join_pond_success</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>metrics+日志</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>join/reconnect 成功</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>pondId
-joinKind</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>{"joinKind":"reconnect"}</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>gameState.ts</t>
+          <t>recordFishingMetric 的顶层参数。不自动写入 payload</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>A连接会话</t>
+          <t>payload</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>join_pond_fail</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>metrics+日志</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>join 失败</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>ackError</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>gameState.ts</t>
+          <t>只含调用时传入的 payload 对象。recordStructuredMetric 会把 playerId、pondId、correlationId 再抄进这份 JSON</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>A连接会话</t>
+          <t>correlation_id</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>leave_pond</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>metrics+日志</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>主动离塘</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>reason</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>{"reason":"user_leave"}</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>gameState.ts</t>
+          <t>若 payload.correlationId 是字符串，复制到本列；JSON 里仍保留该键</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>A连接会话</t>
+          <t>dedup_key</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>disconnect_timeout</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>metrics+日志</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>60s 未重连清场</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>playerId
-pondId</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>fishingStateMachine.ts</t>
+          <t>仅 catch_accept、pending_catch_accept，且 payload.eventId 为非空字符串时写入：{event_type}:{eventId}。冲突则跳过</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>A连接会话</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>session_rebound</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>日志</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>playerId 绑定新 socket</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>playerId
-socketId</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>sessionRegistry.ts</t>
+          <t>写入时的 Date.now()，Unix 毫秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>相位短码</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>f/t/c。f=-1 无来源；0 idle；1 seated；2 baiting；3 casting；4 waiting；5 hooked；6 resolving；7 stopping；8 disconnected；9 groundbaiting</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>整行示例 bite_hook</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>{"id":"&lt;uuid&gt;","event_type":"bite_hook","player_id":"p1","pond_id":"pond-calm","payload":"{\"speciesId\":\"crucian\",\"quality\":\"green\",\"sessionHooks\":1,\"sessionEscapes\":0,\"sessionMissTicks\":4,\"missTicksSinceLastHook\":4,\"waitingMsSinceLastHook\":180000}","correlation_id":null,"dedup_key":null,"created_at":1710000000000}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>整行示例 fishing_phase_transition</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>{"id":"&lt;uuid&gt;","event_type":"fishing_phase_transition","player_id":"p1","pond_id":"pond-calm","payload":"{\"f\":4,\"t\":5,\"c\":\"bite_hook\"}","correlation_id":null,"dedup_key":null,"created_at":1710000000000}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>整行示例 join_pond_success</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>{"id":"&lt;uuid&gt;","event_type":"join_pond_success","player_id":"p1","pond_id":"pond-calm","payload":"{\"userId\":\"u1\",\"socketId\":\"sock-1\",\"spotId\":null,\"fishingPhase\":\"idle\",\"reason\":\"join_pond_success\",\"joinKind\":\"fresh\",\"playerId\":\"p1\",\"pondId\":\"pond-calm\"}","correlation_id":null,"dedup_key":null,"created_at":1710000000000}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>整行示例 pending_catch_accept</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>{"id":"&lt;uuid&gt;","event_type":"pending_catch_accept","player_id":"p1","pond_id":"pond-calm","payload":"{\"speciesId\":\"crucian\",\"quality\":\"green\",\"sizeM\":0.2,\"eventId\":\"catch-1\",\"auto\":false}","correlation_id":null,"dedup_key":"pending_catch_accept:catch-1","created_at":1710000000000}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>不进此表</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>类型为「日志」「聚合日志」「指标+可选日志」的事件只打结构化日志或 Prometheus，不写 fishing_metrics。pond_ecology_catchup 在契约中保留字段，生产只打日志</t>
         </is>
       </c>
     </row>
@@ -3704,17 +4462,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -3768,37 +4526,33 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>B钓位鱼塘</t>
+          <t>A连接会话</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>spot_take_success</t>
+          <t>socket_connect</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>metrics</t>
+          <t>metrics+日志</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>占座成功</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>spotId</t>
-        </is>
-      </c>
+          <t>socket 建连成功，此时尚未绑定玩家</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"socketId":"sock-1","reason":"socket_connected","correlationId":"corr-1"}</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -3808,44 +4562,40 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>gameState.ts</t>
+          <t>socketLifecycle.ts</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>B钓位鱼塘</t>
+          <t>A连接会话</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>spot_take_fail</t>
+          <t>socket_connect_error</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>metrics</t>
+          <t>metrics+日志</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>占座失败</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>reason</t>
-        </is>
-      </c>
+          <t>引擎 connection_error</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"socketId":"sock-1","reason":"xhr poll error","code":1}</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -3855,45 +4605,45 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>gameState.ts</t>
+          <t>socketLifecycle.ts</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>B钓位鱼塘</t>
+          <t>A连接会话</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>spot_release</t>
+          <t>socket_disconnect</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>metrics</t>
+          <t>metrics+日志</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>释放钓位</t>
+          <t>在塘玩家 socket 断开，进入宽限</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>spotId
-reason</t>
+          <t>playerId
+pondId</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"userId":"u1","spotId":"spot-1","fishingPhase":"waiting","reason":"socket_disconnect"}</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -3903,19 +4653,19 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>gameState.ts</t>
+          <t>fishingStateMachine.ts</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>B钓位鱼塘</t>
+          <t>A连接会话</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>pond_full_reject</t>
+          <t>disconnect</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -3925,69 +4675,71 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>鱼塘满</t>
+          <t>旧断线名。生产不再写，测试与历史查询仍认</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>pondId</t>
+          <t>playerId
+pondId</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"socketId":"sock-1","reason":"transport"}</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已废弃</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>gameState.ts</t>
+          <t>fishingStateMachine.ts</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>B钓位鱼塘</t>
+          <t>A连接会话</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>bot_evicted_for_human</t>
+          <t>reconnect</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>metrics</t>
+          <t>metrics+日志</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>踢 bot 腾位</t>
+          <t>宽限期内重连回塘</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>botUserId</t>
+          <t>playerId
+pondId</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"userId":"u1","spotId":"spot-1","fishingPhase":"waiting","reason":"socket_reconnect"}</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -3997,60 +4749,381 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>gameState.ts</t>
+          <t>fishingStateMachine.ts</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>B钓位鱼塘</t>
+          <t>A连接会话</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>pond_ecology_catchup</t>
+          <t>disconnect_timeout</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>metrics+日志</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>断线宽限超时清场</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>{"userId":"u1","spotId":"spot-1","fishingPhase":"disconnected","reason":"disconnect_timeout"}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>fishingStateMachine.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>A连接会话</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>join_pond_attempt</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>metrics+日志</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>收到 join_pond。身份会再抄进 payload</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>{"socketId":"sock-1","reason":"join_pond_attempt","playerId":"p1","pondId":"pond-calm"}</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>socketPondHandlers.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>A连接会话</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>join_pond_success</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>metrics+日志</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>进塘或重连成功。joinKind=fresh|reconnect</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>{"userId":"u1","socketId":"sock-1","spotId":null,"fishingPhase":"idle","reason":"join_pond_success","joinKind":"fresh","playerId":"p1","pondId":"pond-calm"}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>socketPondHandlers.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>A连接会话</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>join_pond_fail</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>metrics+日志</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>进塘失败。reason=return_fee_mode|pond_access|police_ban|pond_full 等</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>{"socketId":"sock-1","reason":"pond_full","ackError":"鱼塘已满（最多 20 人）"}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>socketPondHandlers.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>A连接会话</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>leave_pond</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>主动离塘带会话计数；巡警罚款离塘 reason=police_fine</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>{"reason":"user_explicit","spotId":"spot-1","fishingPhase":"seated","sessionHooks":1,"sessionEscapes":0,"sessionMissTicks":4,"missTicksSinceLastHook":4}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>socketPondHandlers.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>A连接会话</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>session_rebound</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
           <t>日志</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>空鱼塘唤醒时事务化补算生态</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>pondId
-offlineMs
-replaySteps
-migrated
-supplemented
-durationMs
-catchupCompacted</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>{"catchupCompacted":false,"replaySteps":2}</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>同一 playerId 绑到新 socket。不进 fishing_metrics</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+socketId</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>{"playerId":"p1","socketId":"sock-2","previousSocketId":"sock-1","reason":"session_registry_bind_player","correlationId":"corr-1"}</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>pondEcology.ts</t>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>sessionRegistry.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>A连接会话</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>server_start</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 开始监听</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>{"pid":1234,"startedAt":1710000000000,"reason":"unknown"}</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>index.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>A连接会话</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>server_stop</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>收到 SIGINT/SIGTERM 或致命错误，开始停机</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>{"pid":1234,"uptimeSec":3600,"reason":"SIGTERM","startedAt":1710000000000}</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>index.ts</t>
         </is>
       </c>
     </row>
@@ -4065,17 +5138,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -4129,39 +5202,39 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C状态机</t>
+          <t>B钓位鱼塘</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>fishing_phase_transition</t>
+          <t>spot_take_success</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>metrics+日志</t>
+          <t>metrics</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>phase 变更；D-L2-16 metrics 仅短码 f/t/c；ADMIN-OBS-1.3 默认 bot 不落库（METRICS_BOT_PHASE=1 恢复）；日志仍用全称</t>
+          <t>占座成功</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>f
-t
-c</t>
+          <t>playerId
+pondId
+spotId</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>{"f":4,"t":5,"c":"bite_hook"}</t>
+          <t>{"userId":"u1","socketId":"sock-1","spotId":"spot-1","fishingPhase":"seated","eventId":"spot_take:u1:spot-1"}</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -4171,41 +5244,41 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>fishingObservability.ts</t>
+          <t>pondSession.ts</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>C状态机</t>
+          <t>B钓位鱼塘</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>phase_transition_invalid</t>
+          <t>spot_take_fail</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>日志+metrics</t>
+          <t>metrics</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>非法跳转；metrics 短码 f/t/c；日志可读全称</t>
+          <t>钓位已被占用</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>f
-t
-c</t>
+          <t>playerId
+pondId
+spotId</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>{"f":0,"t":5,"c":"bite_hook"}</t>
+          <t>{"userId":"u1","spotId":"spot-1","reason":"occupied_by_human","occupantUserId":"u2","eventId":"spot_fail:u1:spot-1"}</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -4220,7 +5293,245 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>fishingStateMachine.ts</t>
+          <t>pondSession.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>B钓位鱼塘</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>spot_release</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>离席或离塘释放钓位。reason=leave_spot|leave_pond</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId
+spotId</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>{"userId":"u1","spotId":"spot-1","fishingPhase":"idle","reason":"leave_spot","eventId":"spot_release:u1:spot-1:leave_spot"}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>pondSession.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>B钓位鱼塘</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>pond_full_reject</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>人数达到上限</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>{"socketId":"sock-1","reason":"max_pond_users","maxPondUsers":20,"eventId":"pond_full:p1:1710000000000"}</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>pondSession.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>B钓位鱼塘</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>bot_evicted_for_human</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>给人腾位。player_id 列是被挤走的 bot</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>pondId</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>{"userId":"bot-user","reason":"pond_full_or_spot_pressure","eventId":"bot_evict:bot-user:1710000000000"}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>pondUserManager.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>B钓位鱼塘</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>pond_ecology_catchup</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>日志</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>空鱼塘唤醒补算。只打日志，不进 fishing_metrics</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>pondId</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>{"eventType":"pond_ecology_catchup","pondId":"pond-calm","offlineMs":60000,"replaySteps":2,"migrated":0,"supplemented":1,"durationMs":12,"catchupCompacted":false}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>pondEcology.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>B钓位鱼塘</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>pond_ecology_catchup_failed</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>日志</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>进塘前补算失败。只打日志</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>pondId</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>{"eventType":"pond_ecology_catchup_failed","pondId":"pond-calm","playerId":"p1"}</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>socketPondHandlers.ts</t>
         </is>
       </c>
     </row>
@@ -4235,17 +5546,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -4299,80 +5610,87 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>D咬钩产出</t>
+          <t>C状态机</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>bite_tick_miss</t>
+          <t>fishing_phase_transition</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>metrics</t>
+          <t>metrics+日志</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>waiting 未咬钩（D-L2-15 默认不落库；METRICS_BITE_TICK_PERSIST=1）</t>
+          <t>相位变更。库内仅 f/t/c；日志用全名。默认 bot 不落库（METRICS_BOT_PHASE=1 恢复）。f=-1 无来源；0 idle 1 seated 2 baiting 3 casting 4 waiting 5 hooked 6 resolving 7 stopping 8 disconnected 9 groundbaiting</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>pondId</t>
+          <t>playerId
+pondId
+f
+t
+c</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"f":4,"t":5,"c":"bite_hook"}</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>已废弃默认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>fishingStateMachine.ts</t>
+          <t>fishingObservability.ts</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>D咬钩产出</t>
+          <t>C状态机</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>bite_tick_hit</t>
+          <t>phase_transition_invalid</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>metrics</t>
+          <t>metrics+日志</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>waiting 咬钩（D-L2-15 默认不落库，并入 bite_hook）</t>
+          <t>非法相位跳转。库内仅 f/t/c；日志保留全名。默认 bot 不落库</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>speciesId
-quality</t>
+          <t>playerId
+pondId
+f
+t
+c</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"f":0,"t":5,"c":"bite_hook"}</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -4382,437 +5700,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>已废弃默认</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
           <t>fishingStateMachine.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>D咬钩产出</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>bite_hook</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>上钩+会话累计（sessionHooks/Escapes/MissTicks）</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>sessionHooks
-sessionMissTicks</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>fishingStateMachine.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>D咬钩产出</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>pending_catch_created</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>待领取创建</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>fishId</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>inventory.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>D咬钩产出</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>pending_catch_accept</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>领取成功</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>fishId</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>已实现(别名catch_accept)</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>socketPondHandlers.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>D咬钩产出</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>pending_catch_expired</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>待领取超时</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>fishId</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>inventory.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>D咬钩产出</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>bait_depleted</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>饵耗尽</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>baitId</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>fishingStateMachine.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>D咬钩产出</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>escape</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>脱钩+会话累计</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>sessionEscapes
-sessionHooks</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>fishingStateMachine.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>D咬钩产出</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>fishing_start</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>开始钓鱼</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>pondId</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>fishingStateMachine.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>D咬钩产出</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>fishing_stop</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>停止钓鱼</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>pondId</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>fishingStateMachine.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>D咬钩产出</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>abandon_fishing</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>&lt;30s 停止</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>pondId</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>fishingMetrics.ts</t>
         </is>
       </c>
     </row>
@@ -4827,17 +5720,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -4891,12 +5784,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>D成长进度</t>
+          <t>D咬钩产出</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>admission_fee_charged</t>
+          <t>bite_tick_miss</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -4906,46 +5799,45 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>收费塘满2h扣费成功</t>
+          <t>waiting 未咬钩。默认不落库；METRICS_BITE_TICK_PERSIST=1 恢复</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>playerId
-pondId
-feePer2h</t>
+pondId</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>{"feePer2h":200,"chargeIndex":1}</t>
+          <t>{"userId":"u1","spotId":"spot-1","reason":"empty"}</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已废弃默认</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>playerProgress.ts</t>
+          <t>fishingStateMachine.ts</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>D成长进度</t>
+          <t>D咬钩产出</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>fishing_stopped_insufficient_gold</t>
+          <t>bite_tick_hit</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -4955,7 +5847,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>金币不足停钓</t>
+          <t>waiting 咬钩 tick。默认不落库，语义并入 bite_hook；METRICS_BITE_TICK_PERSIST=1 恢复</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -4966,34 +5858,34 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>{"feePer2h":200}</t>
+          <t>{"userId":"u1","spotId":"spot-1","speciesId":"crucian","quality":"green","sizeM":0.2,"hookDurationMs":8000}</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>已实现</t>
+          <t>已废弃默认</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>playerProgress.ts</t>
+          <t>fishingStateMachine.ts</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>D成长进度</t>
+          <t>D咬钩产出</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>onboarding_completed</t>
+          <t>bite_hook</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -5003,17 +5895,18 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>新手引导完成</t>
+          <t>上钩，并写入会话累计</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>playerId</t>
+          <t>playerId
+pondId</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>{"pondId":"pond-novice"}</t>
+          <t>{"speciesId":"crucian","quality":"green","sessionHooks":1,"sessionEscapes":0,"sessionMissTicks":4,"missTicksSinceLastHook":4,"waitingMsSinceLastHook":180000}</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5028,19 +5921,19 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>playerProgress.ts</t>
+          <t>fishingStateMachine.ts</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>D成长进度</t>
+          <t>D咬钩产出</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>pond_proficiency_capped</t>
+          <t>escape</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -5050,7 +5943,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>塘熟练度满/锁满停发塘XP</t>
+          <t>脱钩，并写入会话累计</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -5061,12 +5954,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>{"source":"catch"}</t>
+          <t>{"sessionHooks":1,"sessionEscapes":1,"sessionMissTicks":4}</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -5076,19 +5969,19 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>playerProgress.ts</t>
+          <t>fishingStateMachine.ts</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>D成长进度</t>
+          <t>D咬钩产出</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>gameplay_debug_action</t>
+          <t>escape_streak</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -5098,18 +5991,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>玩法 Debug 菜单操作</t>
+          <t>同一玩家连续脱钩达到 3 次时另写一行</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>playerId
-action</t>
+          <t>playerId</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>{"action":"level_up","ok":true}</t>
+          <t>{"streak":3,"eventId":"escape_streak:p1:1710000000000"}</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5124,19 +6016,19 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>gameplayDebug.ts</t>
+          <t>fishingMetrics.ts</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>D成长进度</t>
+          <t>D咬钩产出</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>fish_returned_to_pond</t>
+          <t>fishing_start</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -5146,7 +6038,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>回鱼入塘增重并发奖</t>
+          <t>开始一局。payload 为空</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -5157,12 +6049,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>{"speciesId":"crucian","sizeM":0.2,"gold":56,"sizeGainM":0.03,"auto":false}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -5172,19 +6064,19 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>returnFish.ts</t>
+          <t>fishingStateMachine.ts</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>D成长进度</t>
+          <t>D咬钩产出</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>return_fee_mode_selected</t>
+          <t>fishing_stop</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -5194,7 +6086,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>进塘双价模式选择</t>
+          <t>收杆。payload 为会话计数</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -5205,7 +6097,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>{"mode":"auto_return","feePer2h":350}</t>
+          <t>{"sessionHooks":2,"sessionEscapes":1,"sessionMissTicks":6,"missTicksSinceLastHook":2}</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5220,19 +6112,19 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>socketPondHandlers.ts</t>
+          <t>fishingStateMachine.ts</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>D成长进度</t>
+          <t>D咬钩产出</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>fish_auto_returned</t>
+          <t>abandon_fishing</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -5242,73 +6134,72 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>达标鱼自动回塘</t>
+          <t>fishing_start 后 30 秒内 fishing_stop。payload 为空</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>fishingMetrics.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>D咬钩产出</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>pending_catch_created</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>锁定待结算的咬钩鱼</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>playerId
 pondId</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>{"speciesId":"crucian","sizeM":0.28,"gold":120,"auto":true}</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>{"userId":"u1","pondFishId":"fish-1","speciesId":"crucian","quality":"green","sizeM":0.2,"hookDurationMs":8000}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>returnFish.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>D成长进度</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>achievement_unlocked</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>成就解锁</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>playerId
-achievementId</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>{"achievementId":"ach-first-catch"}</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>已实现</t>
@@ -5316,19 +6207,19 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>achievements.ts</t>
+          <t>inventory.ts</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>D成长进度</t>
+          <t>D咬钩产出</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>album_pin_changed</t>
+          <t>pending_catch_accept</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -5338,19 +6229,18 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>相册钉选变更</t>
+          <t>收鱼入包。dedup_key=pending_catch_accept:{eventId}</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
           <t>playerId
-pinCount
-action</t>
+pondId</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>{"pinCount":3,"action":"pin"}</t>
+          <t>{"speciesId":"crucian","quality":"green","sizeM":0.2,"eventId":"catch-1","auto":false}</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5365,19 +6255,19 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>album.ts</t>
+          <t>catchSettlement.ts</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>D成长进度</t>
+          <t>D咬钩产出</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>profile_hub_opened</t>
+          <t>pending_catch_expired</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -5387,18 +6277,18 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>打开个人中心</t>
+          <t>待结算超时释放</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>playerId
-tab</t>
+pondId</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>{"tab":"album"}</t>
+          <t>{"userId":"u1","pondFishId":"fish-1","speciesId":"crucian","quality":"green","sizeM":0.2}</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5413,7 +6303,103 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>profileHub.ts</t>
+          <t>inventory.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>D咬钩产出</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>catch_accept</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>旧收鱼名。生产改写 pending_catch_accept；历史榜与测试仍认</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>{"fishId":"fish-1","speciesId":"crucian","quality":"green","sizeM":0.2}</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>已废弃</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>catchSettlement.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>D咬钩产出</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>bait_depleted</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>饵尽。reason=auto_switch_after_depletion|bait_insufficient</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>{"userId":"u1","socketId":"sock-1","previousBaitId":"bait-worm","reason":"auto_switch_after_depletion"}</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>fishingStateMachine.ts</t>
         </is>
       </c>
     </row>
@@ -5428,17 +6414,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -5492,12 +6478,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>D装备</t>
+          <t>D成长进度</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>bait_use</t>
+          <t>admission_fee_charged</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -5507,19 +6493,18 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>咬钩使用进阶饵扣金</t>
+          <t>收费塘满 2 小时扣费成功</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>playerId
-baitId
-cost</t>
+pondId</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>{"baitId":"bait-veg","cost":15}</t>
+          <t>{"feePer2h":200,"returnFeeMode":"sell_only","chargeIndex":1,"progressMs":7200000,"coinsAfter":800}</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -5534,19 +6519,19 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>gear.ts</t>
+          <t>playerProgress.ts</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>D装备</t>
+          <t>D成长进度</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>rod_buy</t>
+          <t>fishing_stopped_insufficient_gold</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -5556,18 +6541,18 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>购买钓竿</t>
+          <t>金币不够支付下一档入场费</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>playerId
-rodId</t>
+pondId</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>{"rodId":"rod-tai","cost":2500}</t>
+          <t>{"feePer2h":200,"returnFeeMode":"sell_only","charges":1,"progressMs":14400000,"coins":0}</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -5582,19 +6567,19 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>shop.ts</t>
+          <t>playerProgress.ts</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>D装备</t>
+          <t>D成长进度</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>rod_broke</t>
+          <t>onboarding_completed</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -5604,18 +6589,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>超规格满N次销毁钓竿</t>
+          <t>新手引导完成。pond_id 列固定 pond-novice</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>playerId
-rodId</t>
+          <t>playerId</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>{"sizeM":0.5,"oversizeLandings":3}</t>
+          <t>{"completedAt":1710000000000}</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5630,19 +6614,19 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>gear.ts</t>
+          <t>playerProgress.ts</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>D装备</t>
+          <t>D成长进度</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>vessel_buy</t>
+          <t>pond_proficiency_capped</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -5652,18 +6636,18 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>购买船具（不可使用）</t>
+          <t>塘熟练度封顶。source=catch|return|duration</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>playerId
-vesselId</t>
+pondId</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>{"vesselId":"vessel-raft","cost":15000}</t>
+          <t>{"pondLevel":10,"playerLevel":8,"source":"catch"}</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5678,19 +6662,19 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>shop.ts</t>
+          <t>playerProgress.ts</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>D装备</t>
+          <t>D成长进度</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>groundbait_cast_started</t>
+          <t>gameplay_debug_action</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -5700,18 +6684,18 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>开始打窝扣金</t>
+          <t>玩法 Debug 菜单</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>playerId
-groundbaitId</t>
+action</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>{"costGold":30,"stackBefore":0}</t>
+          <t>{"action":"level_up","ok":true,"message":"ok"}</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5726,19 +6710,19 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>groundbait.ts</t>
+          <t>gameplayDebug.ts</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>D装备</t>
+          <t>D成长进度</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>groundbait_applied</t>
+          <t>fish_returned_to_pond</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -5748,7 +6732,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>打窝完成叠层</t>
+          <t>回鱼入塘。自动回鱼时再写 fish_auto_returned</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -5759,12 +6743,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>{"stackAfter":1,"biteBonus":0.006}</t>
+          <t>{"speciesId":"crucian","sizeM":0.2,"gold":56,"sizeGainM":0.03,"quality":"green","newSizeM":0.23,"sellGold":40,"spawned":true,"auto":false}</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -5774,19 +6758,19 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>groundbait.ts</t>
+          <t>returnFish.ts</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>D装备</t>
+          <t>D成长进度</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>groundbait_rejected</t>
+          <t>fish_auto_returned</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -5796,18 +6780,18 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>打窝拒绝</t>
+          <t>达标自动回塘。payload 与 fish_returned_to_pond 相同且 auto=true</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>playerId
-reason</t>
+pondId</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>{"reason":"gold","code":"INSUFFICIENT_GOLD"}</t>
+          <t>{"speciesId":"crucian","sizeM":0.28,"gold":120,"sizeGainM":0.04,"quality":"green","newSizeM":0.32,"sellGold":80,"spawned":true,"auto":true}</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5822,7 +6806,243 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>groundbait.ts</t>
+          <t>returnFish.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>D成长进度</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>return_fee_mode_selected</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>进塘选定卖鱼或自动回鱼</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>playerId
+pondId</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>{"mode":"auto_return","feePer2h":350}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>socketPondHandlers.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>D成长进度</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>gold_earn</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>卖鱼 source=fish_sell；回鱼 source=fish_return</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>{"amount":56,"source":"fish_sell","fishId":"inv-1","quality":"green","sizeM":0.2}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>socialRoutes.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>D成长进度</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>achievement_unlocked</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>成就解锁</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>{"achievementId":"ach-first-catch"}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>achievements.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>D成长进度</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>album_pin_changed</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>相册钉选。action=pin|unpin|set</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>{"pinCount":3,"action":"pin"}</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>socialRoutes.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>D成长进度</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>profile_hub_opened</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>打开自己的个人中心。tab 默认 profile</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>{"tab":"profile"}</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>socialRoutes.ts</t>
         </is>
       </c>
     </row>
@@ -5837,17 +7057,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -5901,12 +7121,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>D风险</t>
+          <t>D装备</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>forbidden_pond_fine</t>
+          <t>bait_use</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -5916,81 +7136,456 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>禁止塘巡警超时罚款+当日禁钓</t>
+          <t>咬钩时进阶饵扣金</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>{"baitId":"bait-veg","cost":15,"coinsAfter":985}</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>gear.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>D装备</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>bait_buy</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>旧买饵事件。接口已拒绝，无生产写入</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>{"baitId":"worm","quantity":1,"cost":500}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>已废弃</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>shop.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>D装备</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>tackle_buy</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>旧买渔具事件。生产改写 rod_buy</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>{"tackleId":"rod-basic","cost":100}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>已废弃</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>shop.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>D装备</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>tackle_repair</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>修理渔具</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>{"tackleId":"pro","cost":40}</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>gear.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>D装备</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>rod_buy</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>购买钓竿</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>{"rodId":"rod-tai","cost":2500}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>shop.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>D装备</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>rod_broke</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>超规格次数达到销毁阈值</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>{"rodId":"rod-tai","sizeM":0.5,"oversizeLandings":3}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>gear.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>D装备</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>vessel_buy</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>购买船具（不可使用）</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>{"vesselId":"vessel-raft","cost":15000}</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>shop.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>D装备</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>groundbait_cast_started</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>开始打窝扣金。不写 pond_id</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>{"groundbaitId":"gb-basic","costGold":30,"stackBefore":0}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>groundbait.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>D装备</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>groundbait_applied</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>打窝完成叠层</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>playerId
 pondId</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>{"charged":800,"coinsAfter":0}</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>forbiddenPolice.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>D风险</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>forbidden_pond_escaped</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>metrics</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>禁止塘巡警时限内离塘免罚，2h禁入</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>playerId
-pondId</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>{"untilMs":0}</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>forbiddenPolice.ts</t>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>{"groundbaitId":"gb-basic","stackAfter":1,"biteBonus":0.006,"sizeBonus":0.003}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>groundbait.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>D装备</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>groundbait_rejected</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>metrics</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>打窝被拒绝</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>playerId</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>{"reason":"gold","code":"INSUFFICIENT_GOLD"}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>groundbait.ts</t>
         </is>
       </c>
     </row>
@@ -6005,17 +7600,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -6069,37 +7664,38 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>E性能</t>
+          <t>D风险</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>tick_fishing_phases_duration_ms</t>
+          <t>forbidden_pond_fine</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>聚合日志</t>
+          <t>metrics</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>200ms tick 耗时</t>
+          <t>巡警超时罚款并当日禁钓</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>durationMs</t>
+          <t>playerId
+pondId</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"charged":800,"coinsAfter":0,"fineGold":800,"raidId":"raid-1"}</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -6109,44 +7705,45 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>serverLoops.ts</t>
+          <t>forbiddenPolice.ts</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>E性能</t>
+          <t>D风险</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>bite_check_loop_duration_ms</t>
+          <t>forbidden_pond_escaped</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>聚合日志</t>
+          <t>metrics</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>咬钩循环耗时</t>
+          <t>时限内离塘免罚，2 小时禁入</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>durationMs</t>
+          <t>playerId
+pondId</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"untilMs":1710007200000,"raidId":"raid-1"}</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -6156,201 +7753,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>serverLoops.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>E性能</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>snapshot_build_duration_ms</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>聚合日志</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>buildSnapshot 耗时</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>durationMs
-pondId</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>gameState.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>E性能</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>socket_broadcast_fanout</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>指标+可选日志</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>广播 fanout；默认 Prometheus counter，FANOUT_LOG_INFO=1 才打 info</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>fanoutCount
-channel
-pondId</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>serverLoops.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>E性能</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>sqlite_query_slow</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>日志</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>慢 SQL</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>label
-durationMs
-rows</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>db.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>E性能</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>admin_route_duration_ms</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>日志</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Admin 接口耗时</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>route
-durationMs</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>admin.ts</t>
+          <t>forbiddenPolice.ts</t>
         </is>
       </c>
     </row>
